--- a/Excel/Tabella_pag_dati.xlsx
+++ b/Excel/Tabella_pag_dati.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annar\OneDrive\Desktop\Progetto_Vegna_DH\Sito_web\Dati\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Sito_web\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E374BBE7-8A6F-491D-B5B5-76AABB5EC9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DEC323-ABFA-48D9-A227-5795FDBAB202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89012CC7-AEAA-42E4-9078-2C022CB0F134}"/>
+    <workbookView xWindow="1035" yWindow="2640" windowWidth="21600" windowHeight="11385" xr2:uid="{89012CC7-AEAA-42E4-9078-2C022CB0F134}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,6 @@
     <t>uomo inserisce una scheda elettorale in un'urna sormontata dalla doppia erma di Garibaldi e Stalin</t>
   </si>
   <si>
-    <t>muro con scritta Blocco Nazionale; da una parte del muro vi è una folla di proletari con bandiera comunista; dall’altra parte vi è una famigliola felice, con bimbo che sventola bandiera italiana</t>
-  </si>
-  <si>
     <t>simbolo politico dell'Unità Socialista</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t>data</t>
+  </si>
+  <si>
+    <t>muro con scritta Blocco Nazionale; da una parte del muro vi è una folla di proletari con bandiera comunista; dall’altra parte vi è una famigliola felice con bimbo che sventola bandiera italiana</t>
   </si>
 </sst>
 </file>
@@ -582,30 +582,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A5E440-D03D-44CC-A4CC-52BDC9243CC8}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="64.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -619,7 +619,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -633,7 +633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -647,7 +647,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -658,10 +658,10 @@
         <v>1948</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -672,10 +672,10 @@
         <v>1948</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -686,10 +686,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -700,10 +700,10 @@
         <v>1953</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -714,10 +714,10 @@
         <v>1953</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -728,10 +728,10 @@
         <v>1950</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -742,10 +742,10 @@
         <v>1953</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -756,10 +756,10 @@
         <v>1952</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -770,10 +770,10 @@
         <v>1953</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -784,10 +784,10 @@
         <v>1958</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -798,10 +798,10 @@
         <v>1958</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -812,10 +812,10 @@
         <v>1955</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -826,10 +826,10 @@
         <v>1958</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -840,10 +840,10 @@
         <v>1958</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -854,7 +854,7 @@
         <v>1958</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -884,11 +884,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1048,26 +1049,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1091,9 +1083,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/Tabella_pag_dati.xlsx
+++ b/Excel/Tabella_pag_dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Sito_web\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DEC323-ABFA-48D9-A227-5795FDBAB202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A25CF6-316A-4290-9F18-9B58F6F17A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1035" yWindow="2640" windowWidth="21600" windowHeight="11385" xr2:uid="{89012CC7-AEAA-42E4-9078-2C022CB0F134}"/>
   </bookViews>
@@ -137,9 +137,6 @@
     <t>simbolo politico dell'Unità Socialista</t>
   </si>
   <si>
-    <t>Democrazia Cristiana / Democrazia Cristiana. -; 1948 ?. - 1 volantino (2 p.) : stampa tipografica ; 17x12 cm.Programma elettorale Democrazia Cristiana.Incipit del testo: nell'ora in cui l'Italia rinasce dal sangue... Il foglio è stampato su entrambi i lati; Soggetti: Democrazia Cristiana - Propaganda elettorale - 1948-1955; Gabriotti Venanzio - Democrazia Cristiana</t>
-  </si>
-  <si>
     <t>braccia spazzano cartacce e scarafaggi con il simbolo della Democrazia Cristiana sul dorso</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>figure dirette a un seggio elettorale tra due file di soldati rossi con mitra</t>
   </si>
   <si>
-    <t>Il responso del veggente : canzone valzer allegro sul motivo de "Il Vecchio Pollo". - Roma : Capriotti, 1953. - 1 volantino (2 p. : stampa tipografica ; 25x18 cm. Canzone di propaganda politica anticomunista. - Sul retro il testo originale della canzone. Soggetti: Canti politici - Italia - 1946-1955; Elezioni politiche - Italia - 1953; Nenni Pietro; Togliatti Palmiro; Pajetta Giancarlo</t>
-  </si>
-  <si>
     <t>tre bandiere sbrindellate sventolano issate su una forchetta spuntata</t>
   </si>
   <si>
@@ -186,6 +180,12 @@
   </si>
   <si>
     <t>muro con scritta Blocco Nazionale; da una parte del muro vi è una folla di proletari con bandiera comunista; dall’altra parte vi è una famigliola felice con bimbo che sventola bandiera italiana</t>
+  </si>
+  <si>
+    <t>Democrazia Cristiana / Democrazia Cristiana. -; 1948 ?. - 1 volantino (2 p.) : stampa tipografica ; 17x12 cm. Programma elettorale Democrazia Cristiana.Incipit del testo: nell'ora in cui l'Italia rinasce dal sangue... Il foglio è stampato su entrambi i lati; Soggetti: Democrazia Cristiana - Propaganda elettorale - 1948-1955; Gabriotti Venanzio - Democrazia Cristiana</t>
+  </si>
+  <si>
+    <t>Il responso del veggente : canzone valzer allegro sul motivo de "Il Vecchio Pollo". - Roma : Capriotti. 1953. - 1 volantino (2 p. : stampa tipografica ; 25x18 cm. Canzone di propaganda politica anticomunista. - Sul retro il testo originale della canzone. Soggetti: Canti politici - Italia - 1946-1955; Elezioni politiche - Italia - 1953; Nenni Pietro; Togliatti Palmiro; Pajetta Giancarlo</t>
   </si>
 </sst>
 </file>
@@ -593,13 +593,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
         <v>45</v>
-      </c>
-      <c r="B1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" t="s">
-        <v>47</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
@@ -658,7 +658,7 @@
         <v>1948</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -686,7 +686,7 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -700,7 +700,7 @@
         <v>1953</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -714,7 +714,7 @@
         <v>1953</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -728,7 +728,7 @@
         <v>1950</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -742,7 +742,7 @@
         <v>1953</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,7 +756,7 @@
         <v>1952</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -770,7 +770,7 @@
         <v>1953</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -784,7 +784,7 @@
         <v>1958</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -798,7 +798,7 @@
         <v>1958</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -812,7 +812,7 @@
         <v>1955</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -826,7 +826,7 @@
         <v>1958</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -840,7 +840,7 @@
         <v>1958</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -854,7 +854,7 @@
         <v>1958</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -884,12 +884,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1049,17 +1048,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1083,17 +1091,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/Tabella_pag_dati.xlsx
+++ b/Excel/Tabella_pag_dati.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Sito_web\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A25CF6-316A-4290-9F18-9B58F6F17A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215580C3-C48E-4598-B055-0386120F25DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1035" yWindow="2640" windowWidth="21600" windowHeight="11385" xr2:uid="{89012CC7-AEAA-42E4-9078-2C022CB0F134}"/>
   </bookViews>
@@ -179,13 +179,13 @@
     <t>data</t>
   </si>
   <si>
-    <t>muro con scritta Blocco Nazionale; da una parte del muro vi è una folla di proletari con bandiera comunista; dall’altra parte vi è una famigliola felice con bimbo che sventola bandiera italiana</t>
-  </si>
-  <si>
-    <t>Democrazia Cristiana / Democrazia Cristiana. -; 1948 ?. - 1 volantino (2 p.) : stampa tipografica ; 17x12 cm. Programma elettorale Democrazia Cristiana.Incipit del testo: nell'ora in cui l'Italia rinasce dal sangue... Il foglio è stampato su entrambi i lati; Soggetti: Democrazia Cristiana - Propaganda elettorale - 1948-1955; Gabriotti Venanzio - Democrazia Cristiana</t>
-  </si>
-  <si>
-    <t>Il responso del veggente : canzone valzer allegro sul motivo de "Il Vecchio Pollo". - Roma : Capriotti. 1953. - 1 volantino (2 p. : stampa tipografica ; 25x18 cm. Canzone di propaganda politica anticomunista. - Sul retro il testo originale della canzone. Soggetti: Canti politici - Italia - 1946-1955; Elezioni politiche - Italia - 1953; Nenni Pietro; Togliatti Palmiro; Pajetta Giancarlo</t>
+    <t>muro con scritta Blocco Nazionale. da una parte del muro vi è una folla di proletari con bandiera comunista; dall’altra parte vi è una famigliola felice con bimbo che sventola bandiera italiana</t>
+  </si>
+  <si>
+    <t>Democrazia Cristiana / Democrazia Cristiana. -. 1948 ?. - 1 volantino (2 p.) : stampa tipografica . 17x12 cm. Programma elettorale Democrazia Cristiana. Incipit del testo: nell'ora in cui l'Italia rinasce dal sangue... Il foglio è stampato su entrambi i lati. Soggetti: Democrazia Cristiana - Propaganda elettorale - 1948-1955. Gabriotti Venanzio - Democrazia Cristiana</t>
+  </si>
+  <si>
+    <t>Il responso del veggente : canzone valzer allegro sul motivo de "Il Vecchio Pollo". - Roma : Capriotti. 1953. - 1 volantino (2 p. : stampa tipografica . 25x18 cm. Canzone di propaganda politica anticomunista. - Sul retro il testo originale della canzone. Soggetti: Canti politici - Italia - 1946-1955. Elezioni politiche - Italia - 1953. Nenni Pietro. Togliatti Palmiro. Pajetta Giancarlo</t>
   </si>
 </sst>
 </file>
@@ -884,11 +884,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1048,26 +1049,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1091,9 +1083,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/Tabella_pag_dati.xlsx
+++ b/Excel/Tabella_pag_dati.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Sito_web\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annar\OneDrive\Desktop\Progetto_Vegna_DH\Sito_web\Dati\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215580C3-C48E-4598-B055-0386120F25DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E374BBE7-8A6F-491D-B5B5-76AABB5EC9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="2640" windowWidth="21600" windowHeight="11385" xr2:uid="{89012CC7-AEAA-42E4-9078-2C022CB0F134}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89012CC7-AEAA-42E4-9078-2C022CB0F134}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,15 @@
     <t>uomo inserisce una scheda elettorale in un'urna sormontata dalla doppia erma di Garibaldi e Stalin</t>
   </si>
   <si>
+    <t>muro con scritta Blocco Nazionale; da una parte del muro vi è una folla di proletari con bandiera comunista; dall’altra parte vi è una famigliola felice, con bimbo che sventola bandiera italiana</t>
+  </si>
+  <si>
     <t>simbolo politico dell'Unità Socialista</t>
   </si>
   <si>
+    <t>Democrazia Cristiana / Democrazia Cristiana. -; 1948 ?. - 1 volantino (2 p.) : stampa tipografica ; 17x12 cm.Programma elettorale Democrazia Cristiana.Incipit del testo: nell'ora in cui l'Italia rinasce dal sangue... Il foglio è stampato su entrambi i lati; Soggetti: Democrazia Cristiana - Propaganda elettorale - 1948-1955; Gabriotti Venanzio - Democrazia Cristiana</t>
+  </si>
+  <si>
     <t>braccia spazzano cartacce e scarafaggi con il simbolo della Democrazia Cristiana sul dorso</t>
   </si>
   <si>
@@ -152,6 +158,9 @@
     <t>figure dirette a un seggio elettorale tra due file di soldati rossi con mitra</t>
   </si>
   <si>
+    <t>Il responso del veggente : canzone valzer allegro sul motivo de "Il Vecchio Pollo". - Roma : Capriotti, 1953. - 1 volantino (2 p. : stampa tipografica ; 25x18 cm. Canzone di propaganda politica anticomunista. - Sul retro il testo originale della canzone. Soggetti: Canti politici - Italia - 1946-1955; Elezioni politiche - Italia - 1953; Nenni Pietro; Togliatti Palmiro; Pajetta Giancarlo</t>
+  </si>
+  <si>
     <t>tre bandiere sbrindellate sventolano issate su una forchetta spuntata</t>
   </si>
   <si>
@@ -177,15 +186,6 @@
   </si>
   <si>
     <t>data</t>
-  </si>
-  <si>
-    <t>muro con scritta Blocco Nazionale. da una parte del muro vi è una folla di proletari con bandiera comunista; dall’altra parte vi è una famigliola felice con bimbo che sventola bandiera italiana</t>
-  </si>
-  <si>
-    <t>Democrazia Cristiana / Democrazia Cristiana. -. 1948 ?. - 1 volantino (2 p.) : stampa tipografica . 17x12 cm. Programma elettorale Democrazia Cristiana. Incipit del testo: nell'ora in cui l'Italia rinasce dal sangue... Il foglio è stampato su entrambi i lati. Soggetti: Democrazia Cristiana - Propaganda elettorale - 1948-1955. Gabriotti Venanzio - Democrazia Cristiana</t>
-  </si>
-  <si>
-    <t>Il responso del veggente : canzone valzer allegro sul motivo de "Il Vecchio Pollo". - Roma : Capriotti. 1953. - 1 volantino (2 p. : stampa tipografica . 25x18 cm. Canzone di propaganda politica anticomunista. - Sul retro il testo originale della canzone. Soggetti: Canti politici - Italia - 1946-1955. Elezioni politiche - Italia - 1953. Nenni Pietro. Togliatti Palmiro. Pajetta Giancarlo</t>
   </si>
 </sst>
 </file>
@@ -582,30 +582,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A5E440-D03D-44CC-A4CC-52BDC9243CC8}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="64.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -619,7 +619,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -633,7 +633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -647,7 +647,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -658,10 +658,10 @@
         <v>1948</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -672,10 +672,10 @@
         <v>1948</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -686,10 +686,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -700,10 +700,10 @@
         <v>1953</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -714,10 +714,10 @@
         <v>1953</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -728,10 +728,10 @@
         <v>1950</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -742,10 +742,10 @@
         <v>1953</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -756,10 +756,10 @@
         <v>1952</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -770,10 +770,10 @@
         <v>1953</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -784,10 +784,10 @@
         <v>1958</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -798,10 +798,10 @@
         <v>1958</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -812,10 +812,10 @@
         <v>1955</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -826,10 +826,10 @@
         <v>1958</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -840,10 +840,10 @@
         <v>1958</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -854,7 +854,7 @@
         <v>1958</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -884,12 +884,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1049,17 +1048,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1083,17 +1091,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/Tabella_pag_dati.xlsx
+++ b/Excel/Tabella_pag_dati.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annar\OneDrive\Desktop\Progetto_Vegna_DH\Sito_web\Dati\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Sito_web\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E374BBE7-8A6F-491D-B5B5-76AABB5EC9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAAD679-C289-4F8B-BAA4-487C36306858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{89012CC7-AEAA-42E4-9078-2C022CB0F134}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{89012CC7-AEAA-42E4-9078-2C022CB0F134}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>simbolo politico dell'Unità Socialista</t>
   </si>
   <si>
-    <t>Democrazia Cristiana / Democrazia Cristiana. -; 1948 ?. - 1 volantino (2 p.) : stampa tipografica ; 17x12 cm.Programma elettorale Democrazia Cristiana.Incipit del testo: nell'ora in cui l'Italia rinasce dal sangue... Il foglio è stampato su entrambi i lati; Soggetti: Democrazia Cristiana - Propaganda elettorale - 1948-1955; Gabriotti Venanzio - Democrazia Cristiana</t>
-  </si>
-  <si>
     <t>braccia spazzano cartacce e scarafaggi con il simbolo della Democrazia Cristiana sul dorso</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t>data</t>
+  </si>
+  <si>
+    <t>Democrazia Cristiana / Democrazia Cristiana. -; 1948 ?. - 1 volantino (2 p.) : stampa tipografica ; 17x12 cm.Programma elettorale Democrazia Cristiana. Incipit del testo: nell'ora in cui l'Italia rinasce dal sangue... Il foglio è stampato su entrambi i lati; Soggetti: Democrazia Cristiana - Propaganda elettorale - 1948-1955; Gabriotti Venanzio - Democrazia Cristiana</t>
   </si>
 </sst>
 </file>
@@ -582,30 +582,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A5E440-D03D-44CC-A4CC-52BDC9243CC8}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="64.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>48</v>
       </c>
       <c r="D1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -619,7 +619,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -633,7 +633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -647,7 +647,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -661,7 +661,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -675,7 +675,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -686,10 +686,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -700,10 +700,10 @@
         <v>1953</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -714,10 +714,10 @@
         <v>1953</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -728,10 +728,10 @@
         <v>1950</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -742,10 +742,10 @@
         <v>1953</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -756,10 +756,10 @@
         <v>1952</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -770,10 +770,10 @@
         <v>1953</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -784,10 +784,10 @@
         <v>1958</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -798,10 +798,10 @@
         <v>1958</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -812,10 +812,10 @@
         <v>1955</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -826,10 +826,10 @@
         <v>1958</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -840,10 +840,10 @@
         <v>1958</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -854,7 +854,7 @@
         <v>1958</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -884,11 +884,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1048,26 +1049,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ec621e79-30a5-40a0-82cf-20feb35471e6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1091,9 +1083,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{190AD868-19C8-47CD-99B3-295DECD82A0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{788C1929-E3C1-47C2-8A52-7A99C4307D69}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="ec621e79-30a5-40a0-82cf-20feb35471e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>